--- a/documenten/beheer/Planning-GSTEM.xlsx
+++ b/documenten/beheer/Planning-GSTEM.xlsx
@@ -792,12 +792,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Exacte 9-DoF IMU met sensorfusie kiezen (BNO055 kandidaat)</t>
+          <t>Exacte 9-DoF IMU met sensorfusie kiezen (BNO085)</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>IMU-keuze open</t>
+          <t>Gekozen: Adafruit BNO085</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>open vraag</t>
+          <t>Gekozen: BMP581 en Quectel LC29HDA-breakout</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Exacte breakout-modellen en pinouts bepalen</t>
+          <t>Exacte breakout-modellen, afmetingen en pinouts bepalen</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>bepaalt footprints draagprint</t>
+          <t>Bepaalt handbedrading en montage in behuizing; niet langer PCB-footprints</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Level shifter en I2C-pull-ups uitzoeken (3,3 V vs 5 V)</t>
+          <t>Level shifter en I2C-pull-ups vastleggen</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>open vraag</t>
+          <t>TXB0108-breakout gekozen; geen extra pull-ups; bedrading blijft uit te werken</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Socket-header of alternatief kiezen (precisie-sockets, direct, castellated)</t>
+          <t>Bedrade verbinding kiezen: breakoutmodules zelf bedraden en solderen</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>bepaalt landpatronen</t>
+          <t>Besloten 09/10/2026; sockets en carrier-PCB vervallen</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>PCB-ontwerpgereedschap (KiCad?) en fabrikant kiezen</t>
+          <t>Bedradings- en montagemethode voor elektronica bepalen</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>open vraag</t>
+          <t>Geen eigen carrier-PCB; montage aan 3D-geprinte behuizing</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Bestelformulier afronden en componenten + PCB bestellen</t>
+          <t>Bestellijst afronden voor actieve componenten; geen PCB of sockets bestellen</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>koppelt aan 29/09/2026</t>
+          <t>Behuizingshardware en externe connectoren pas bepalen na montageontwerp</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Draagprint ontwerpen: schema, layout, afmetingen, laagcount, connectoren</t>
+          <t>Handbedrade verbindingen uitwerken: pinout, draadroute en soldeerverbindingen</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>hangt af van pinouts</t>
+          <t>Geen schema/layout voor carrier-PCB; ondersteuning en trekontlasting bepalen</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Behuizing 3D-ontwerpen (PETG/PLA met rubberdemping)</t>
+          <t>3D-behuizing ontwerpen voor directe montage van modules en bedrade elektronica</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>mechanisch ontwerp</t>
+          <t>Materiaal, demping, antennes, luchtdrukopening en bevestiging bepalen</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>PCB assembleren, modules plaatsen, voeding en power-LED doormeten</t>
+          <t>Modules bedraden en solderen; voeding, UART, isolatie en montage controleren</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>hardware klaar</t>
+          <t>Geen PCB-assemblage; controleren na vastleggen bedradings- en montageplan</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
